--- a/docs/downloads/经营分_河南省区__河南东片区_2026-10-18.xlsx
+++ b/docs/downloads/经营分_河南省区__河南东片区_2026-10-18.xlsx
@@ -779,17 +779,17 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>6720495177506572296</t>
+          <t>6774901174207334400</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>维也纳3好酒店(商丘永城东方大道店)</t>
+          <t>希岸酒店（商丘高铁站正弘汇店）</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>维也纳3好酒店(河南永城东方大道店)</t>
+          <t>希岸酒店(商丘高铁站店)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -798,10 +798,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I3" t="n">
-        <v>-3</v>
+        <v>3</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
         <v>10</v>
       </c>
       <c r="M3" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="N3" t="n">
         <v>30</v>
@@ -867,17 +867,17 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>6774901174207334400</t>
+          <t>6720495177506572296</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>希岸酒店（商丘高铁站正弘汇店）</t>
+          <t>维也纳3好酒店(商丘永城东方大道店)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>希岸酒店(商丘高铁站店)</t>
+          <t>维也纳3好酒店(河南永城东方大道店)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -886,10 +886,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="I4" t="n">
-        <v>8</v>
+        <v>-3</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>10</v>
       </c>
       <c r="M4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="N4" t="n">
         <v>30</v>
@@ -915,7 +915,7 @@
         <v>30</v>
       </c>
       <c r="Q4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="R4" t="n">
         <v>30</v>
@@ -1065,7 +1065,7 @@
         <v>92</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>100</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1918,22 +1918,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>开封市</t>
+          <t>商丘市</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>7300115647382423564</t>
+          <t>7121606869444986884</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>锦江之星(开封兰考焦裕禄纪念馆酒店)</t>
+          <t>维也纳酒店（商丘民权高新区火车站店）</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>锦江之星(开封兰考焦裕禄纪念馆店)</t>
+          <t>维也纳酒店(民权高新区火车站店)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1945,7 +1945,7 @@
         <v>110</v>
       </c>
       <c r="I16" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -2006,22 +2006,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>商丘市</t>
+          <t>开封市</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>6601168007412582403</t>
+          <t>7300115647382423564</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>锦江之星品尚（商丘柘城未来大道酒店）</t>
+          <t>锦江之星(开封兰考焦裕禄纪念馆酒店)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>锦江之星品尚(柘城未来大道客运中心店)</t>
+          <t>锦江之星(开封兰考焦裕禄纪念馆店)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2033,11 +2033,11 @@
         <v>110</v>
       </c>
       <c r="I17" t="n">
-        <v>-5</v>
+        <v>5</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>拿收益</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -2047,7 +2047,7 @@
         <v>10</v>
       </c>
       <c r="M17" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N17" t="n">
         <v>30</v>
@@ -2059,7 +2059,7 @@
         <v>30</v>
       </c>
       <c r="Q17" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="R17" t="n">
         <v>30</v>
@@ -2094,27 +2094,27 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>开封市</t>
+          <t>商丘市</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>7177769550258112527</t>
+          <t>6601168007412582403</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>锦江之星风尚（开封通许金达国际建材城富民路店）</t>
+          <t>锦江之星品尚（商丘柘城未来大道酒店）</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>锦江之星酒店(开封通许金达国际建材城富民路店)</t>
+          <t>锦江之星品尚(柘城未来大道客运中心店)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -2135,7 +2135,7 @@
         <v>10</v>
       </c>
       <c r="M18" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N18" t="n">
         <v>30</v>
@@ -2147,7 +2147,7 @@
         <v>30</v>
       </c>
       <c r="Q18" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="R18" t="n">
         <v>30</v>
@@ -2182,34 +2182,34 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>商丘市</t>
+          <t>开封市</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>6694059524057286669</t>
+          <t>7177769550258112527</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>麗枫酒店（商丘高铁站正弘汇店）</t>
+          <t>锦江之星风尚（开封通许金达国际建材城富民路店）</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>麗枫酒店(商丘高铁站正弘汇店)</t>
+          <t>锦江之星酒店(开封通许金达国际建材城富民路店)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H19" t="n">
         <v>110</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -2275,17 +2275,17 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>7227034144323143713</t>
+          <t>6694059524057286669</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>亦岚酒店 （商丘神火大道万达广场店）</t>
+          <t>麗枫酒店（商丘高铁站正弘汇店）</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>亦岚酒店(商丘市政府万达广场店)</t>
+          <t>麗枫酒店(商丘高铁站正弘汇店)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2294,14 +2294,14 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="I20" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>稳房源</t>
+          <t>拿收益</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -2311,7 +2311,7 @@
         <v>10</v>
       </c>
       <c r="M20" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N20" t="n">
         <v>30</v>
@@ -2323,7 +2323,7 @@
         <v>30</v>
       </c>
       <c r="Q20" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="R20" t="n">
         <v>30</v>
@@ -2358,22 +2358,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>开封市</t>
+          <t>商丘市</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>7234796822647031846</t>
+          <t>7227034144323143713</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>潮漫酒店(开封通许县政府店)</t>
+          <t>亦岚酒店 （商丘神火大道万达广场店）</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>潮漫酒店(开封通许县政府店)</t>
+          <t>亦岚酒店(商丘市政府万达广场店)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2385,11 +2385,11 @@
         <v>115</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>拿收益</t>
+          <t>稳房源</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -2399,7 +2399,7 @@
         <v>10</v>
       </c>
       <c r="M21" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N21" t="n">
         <v>30</v>
@@ -2411,7 +2411,7 @@
         <v>30</v>
       </c>
       <c r="Q21" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="R21" t="n">
         <v>30</v>
@@ -2446,22 +2446,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>商丘市</t>
+          <t>开封市</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>7214424032895043642</t>
+          <t>7234796822647031846</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>维也纳国际酒店(5.0商丘虞城嵩山大道店)</t>
+          <t>潮漫酒店(开封通许县政府店)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>维也纳国际酒店(5.0版本虞城嵩山大道店)</t>
+          <t>潮漫酒店(开封通许县政府店)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2473,7 +2473,7 @@
         <v>115</v>
       </c>
       <c r="I22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -2539,17 +2539,17 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>7306778753554712591</t>
+          <t>7214424032895043642</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>维也纳酒店（5.0商丘民权高铁站店）</t>
+          <t>维也纳国际酒店(5.0商丘虞城嵩山大道店)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>维也纳酒店(民权高铁站店)</t>
+          <t>维也纳国际酒店(5.0版本虞城嵩山大道店)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2561,7 +2561,7 @@
         <v>115</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -2627,17 +2627,17 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>7121606869444986884</t>
+          <t>7306778753554712591</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>维也纳酒店（商丘民权高新区火车站店）</t>
+          <t>维也纳酒店（5.0商丘民权高铁站店）</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>维也纳酒店(民权高新区火车站店)</t>
+          <t>维也纳酒店(民权高铁站店)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2649,7 +2649,7 @@
         <v>115</v>
       </c>
       <c r="I24" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H28" t="n">
